--- a/output/pdf_financials_xlsx/NIOB.xlsx
+++ b/output/pdf_financials_xlsx/NIOB.xlsx
@@ -2706,13 +2706,13 @@
         <v>-0.008152</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.161269</v>
+        <v>-0.041022</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.93327</v>
+        <v>0.881905</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.348881</v>
       </c>
     </row>
     <row r="119">
@@ -4862,7 +4862,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NIOB.xlsx
+++ b/output/pdf_financials_xlsx/NIOB.xlsx
@@ -1079,16 +1079,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.058606</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.004234</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.025033</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>5.651259</v>
       </c>
     </row>
     <row r="35">
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.058606</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.004234</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.025033</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>5.651259</v>
       </c>
     </row>
     <row r="37">
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.058606</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.022396</v>
+        <v>0.018162</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.025033</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>5.899266</v>
+        <v>0.248007</v>
       </c>
     </row>
     <row r="49">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">

--- a/output/pdf_financials_xlsx/NIOB.xlsx
+++ b/output/pdf_financials_xlsx/NIOB.xlsx
@@ -1720,10 +1720,10 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0465</v>
       </c>
     </row>
     <row r="68">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.091672</v>
       </c>
     </row>
     <row r="116">
@@ -4898,7 +4898,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
